--- a/Planilhas_importação/Importacao_parcelas.xlsx
+++ b/Planilhas_importação/Importacao_parcelas.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -178,7 +178,11 @@
           </rPr>
           <t xml:space="preserve">Obrigatório. Informe o status atual da parcela, utilizando uma das nomenclaturas abaixo:
 - ABERTA
-- LIQUIDADA</t>
+- LIQUIDADA
+- PRORROGADA
+- ANTECIPADA
+- CANCELADA
+</t>
         </r>
       </text>
     </comment>
@@ -336,14 +340,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFD7"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFBBE6FE"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -356,7 +360,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="31">
+  <cellStyleXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -413,6 +417,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -436,7 +443,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="17">
+  <cellStyles count="18">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -454,6 +461,7 @@
     <cellStyle name="Normal" xfId="28"/>
     <cellStyle name="Título de tabela" xfId="29"/>
     <cellStyle name="Índice" xfId="30"/>
+    <cellStyle name="caption" xfId="31"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -475,8 +483,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFD7"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFBBE6FE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -498,7 +506,7 @@
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF34B3FB"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -630,7 +638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.57"/>

--- a/Planilhas_importação/Importacao_parcelas.xlsx
+++ b/Planilhas_importação/Importacao_parcelas.xlsx
@@ -331,7 +331,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,12 +342,6 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
         <bgColor rgb="FF00CCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE6FE"/>
-        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +428,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -452,16 +446,16 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Body Text" xfId="20"/>
     <cellStyle name="Caption" xfId="21"/>
-    <cellStyle name="Caracteres de nota de fim" xfId="22"/>
-    <cellStyle name="Caracteres de nota de rodapé" xfId="23"/>
-    <cellStyle name="Conteúdo da lista" xfId="24"/>
-    <cellStyle name="Conteúdo da tabela" xfId="25"/>
-    <cellStyle name="FollowedHyperlink" xfId="26"/>
-    <cellStyle name="List" xfId="27"/>
-    <cellStyle name="Normal" xfId="28"/>
-    <cellStyle name="Título de tabela" xfId="29"/>
-    <cellStyle name="Índice" xfId="30"/>
-    <cellStyle name="caption" xfId="31"/>
+    <cellStyle name="caption 1" xfId="22"/>
+    <cellStyle name="Caracteres de nota de fim" xfId="23"/>
+    <cellStyle name="Caracteres de nota de rodapé" xfId="24"/>
+    <cellStyle name="Conteúdo da lista" xfId="25"/>
+    <cellStyle name="Conteúdo da tabela" xfId="26"/>
+    <cellStyle name="FollowedHyperlink" xfId="27"/>
+    <cellStyle name="List" xfId="28"/>
+    <cellStyle name="Normal" xfId="29"/>
+    <cellStyle name="Título de tabela" xfId="30"/>
+    <cellStyle name="Índice" xfId="31"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -484,7 +478,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFBBE6FE"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
